--- a/excel/d-l-f-medina-rivera-s-a_ccc.xlsx
+++ b/excel/d-l-f-medina-rivera-s-a_ccc.xlsx
@@ -1501,7 +1501,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>61819</v>
+        <v>62490</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1535,12 +1535,12 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>C001759624</t>
+          <t>C004024351</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>C001759624 - CEBREROS CORONACION GLORIA MARINA</t>
+          <t>C004024351 - ROJAS TIRADO ROBIN LENIN</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1560,11 +1560,11 @@
         <v>46235</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>S17777809</t>
+          <t>S17828221</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1617,7 +1617,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>62490</v>
+        <v>61819</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -1651,12 +1651,12 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>C004024351</t>
+          <t>C001759624</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>C004024351 - ROJAS TIRADO ROBIN LENIN</t>
+          <t>C001759624 - CEBREROS CORONACION GLORIA MARINA</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1676,11 +1676,11 @@
         <v>46235</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>46246</v>
+        <v>46245</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>S17828221</t>
+          <t>S17777809</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -3565,16 +3565,16 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>12738</v>
+        <v>14681</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>VALERIA ALEXANDRA MONTOYA MANRIQUE</t>
+          <t>LUIS ENRIQUE FERNANDEZ SAAVEDRA</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>74841681</t>
+          <t>43565842</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3599,12 +3599,12 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>C001265255</t>
+          <t>C001326861</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>C001265255 - RODRIGUEZ BALLON MARIA LUISA MILAGROS</t>
+          <t>C001326861 - HERRERA ROMERO MIGUEL ANGEL</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3624,11 +3624,11 @@
         <v>46235</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>46242</v>
+        <v>46246</v>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>S17714575</t>
+          <t>S17821166</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3638,11 +3638,11 @@
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>74841681LIMAVIZARRETA SANCHEZ, ELIZABETH DAYANA1000037029</t>
+          <t>43565842LIMAVIZARRETA SANCHEZ, ELIZABETH DAYANA1000037029</t>
         </is>
       </c>
       <c r="R28" t="n">
-        <v>30</v>
+        <v>57</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
@@ -3651,7 +3651,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Está esperando promociones, descuentos o condiciones más favorables.</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -3669,7 +3669,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Revisar despacho</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3681,16 +3681,16 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>14681</v>
+        <v>12738</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>LUIS ENRIQUE FERNANDEZ SAAVEDRA</t>
+          <t>VALERIA ALEXANDRA MONTOYA MANRIQUE</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>43565842</t>
+          <t>74841681</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3715,12 +3715,12 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>C001326861</t>
+          <t>C001265255</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>C001326861 - HERRERA ROMERO MIGUEL ANGEL</t>
+          <t>C001265255 - RODRIGUEZ BALLON MARIA LUISA MILAGROS</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3740,11 +3740,11 @@
         <v>46235</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>46246</v>
+        <v>46242</v>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>S17821166</t>
+          <t>S17714575</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3754,11 +3754,11 @@
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>43565842LIMAVIZARRETA SANCHEZ, ELIZABETH DAYANA1000037029</t>
+          <t>74841681LIMAVIZARRETA SANCHEZ, ELIZABETH DAYANA1000037029</t>
         </is>
       </c>
       <c r="R29" t="n">
-        <v>57</v>
+        <v>30</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
@@ -3767,7 +3767,7 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>Está esperando promociones, descuentos o condiciones más favorables.</t>
+          <t>-</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>Revisar despacho</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3913,16 +3913,16 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>47547</v>
+        <v>35684</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>LUIS ENRIQUE FERNANDEZ SAAVEDRA</t>
+          <t>VALERIA ALEXANDRA MONTOYA MANRIQUE</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>43565842</t>
+          <t>74841681</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -3937,22 +3937,22 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>No tiene tiempo para capacitarse</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>C001746515</t>
+          <t>C001573709</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>C001746515 - MARIN GARCIA LILI MARDELI</t>
+          <t>C001573709 - MALLQUI PINILLOS SARA CLAUDINA</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -3972,11 +3972,11 @@
         <v>46235</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>46246</v>
+        <v>46244</v>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>S17825118</t>
+          <t>S17748787</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -3986,11 +3986,11 @@
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>43565842LIMAVIZARRETA SANCHEZ, ELIZABETH DAYANA1000037029</t>
+          <t>74841681LIMAVIZARRETA SANCHEZ, ELIZABETH DAYANA1000037029</t>
         </is>
       </c>
       <c r="R31" t="n">
-        <v>57</v>
+        <v>30</v>
       </c>
       <c r="S31" t="inlineStr">
         <is>
@@ -3999,7 +3999,7 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>Está esperando promociones, descuentos o condiciones más favorables.</t>
+          <t>-</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -4010,35 +4010,23 @@
       <c r="V31" t="inlineStr"/>
       <c r="W31" t="inlineStr"/>
       <c r="X31" t="inlineStr"/>
-      <c r="Y31" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>Revisar despacho</t>
-        </is>
-      </c>
-      <c r="AA31" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="Y31" t="inlineStr"/>
+      <c r="Z31" t="inlineStr"/>
+      <c r="AA31" t="inlineStr"/>
       <c r="AB31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>35684</v>
+        <v>47547</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>VALERIA ALEXANDRA MONTOYA MANRIQUE</t>
+          <t>LUIS ENRIQUE FERNANDEZ SAAVEDRA</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>74841681</t>
+          <t>43565842</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4053,22 +4041,22 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>No tiene tiempo para capacitarse</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>C001573709</t>
+          <t>C001746515</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>C001573709 - MALLQUI PINILLOS SARA CLAUDINA</t>
+          <t>C001746515 - MARIN GARCIA LILI MARDELI</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -4088,11 +4076,11 @@
         <v>46235</v>
       </c>
       <c r="N32" s="3" t="n">
-        <v>46244</v>
+        <v>46246</v>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>S17748787</t>
+          <t>S17825118</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4102,11 +4090,11 @@
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>74841681LIMAVIZARRETA SANCHEZ, ELIZABETH DAYANA1000037029</t>
+          <t>43565842LIMAVIZARRETA SANCHEZ, ELIZABETH DAYANA1000037029</t>
         </is>
       </c>
       <c r="R32" t="n">
-        <v>30</v>
+        <v>57</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
@@ -4115,7 +4103,7 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Está esperando promociones, descuentos o condiciones más favorables.</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -4126,9 +4114,21 @@
       <c r="V32" t="inlineStr"/>
       <c r="W32" t="inlineStr"/>
       <c r="X32" t="inlineStr"/>
-      <c r="Y32" t="inlineStr"/>
-      <c r="Z32" t="inlineStr"/>
-      <c r="AA32" t="inlineStr"/>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>Revisar despacho</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
       <c r="AB32" t="inlineStr"/>
     </row>
     <row r="33">
@@ -5165,16 +5165,16 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>81109</v>
+        <v>83450</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>LUIS ENRIQUE FERNANDEZ SAAVEDRA</t>
+          <t>VALERIA ALEXANDRA MONTOYA MANRIQUE</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>43565842</t>
+          <t>74841681</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5199,12 +5199,12 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>C004191510</t>
+          <t>C004182700</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>C004191510 - DAMIAN SANTISTEBAN ESTHER</t>
+          <t>C004182700 - HUACRE CCASANI ANTONIO</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -5224,11 +5224,11 @@
         <v>46235</v>
       </c>
       <c r="N42" s="3" t="n">
-        <v>46246</v>
+        <v>46242</v>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>S17807260</t>
+          <t>S17722037</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -5238,11 +5238,11 @@
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>43565842LIMAVIZARRETA SANCHEZ, ELIZABETH DAYANA1000037029</t>
+          <t>74841681LIMAVIZARRETA SANCHEZ, ELIZABETH DAYANA1000037029</t>
         </is>
       </c>
       <c r="R42" t="n">
-        <v>57</v>
+        <v>30</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
@@ -5251,7 +5251,7 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>Está esperando promociones, descuentos o condiciones más favorables.</t>
+          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -5264,12 +5264,12 @@
       <c r="X42" t="inlineStr"/>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>Revisar despacho</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5281,16 +5281,16 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>83450</v>
+        <v>83665</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>VALERIA ALEXANDRA MONTOYA MANRIQUE</t>
+          <t>LUIS ENRIQUE FERNANDEZ SAAVEDRA</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>74841681</t>
+          <t>43565842</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5315,12 +5315,12 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>C004182700</t>
+          <t>C001759933</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>C004182700 - HUACRE CCASANI ANTONIO</t>
+          <t>C001759933 - HIJAR ZEVALLOS MAGDALENA URBANA</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -5344,7 +5344,7 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>S17722037</t>
+          <t>S17718690</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -5354,11 +5354,11 @@
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>74841681LIMAVIZARRETA SANCHEZ, ELIZABETH DAYANA1000037029</t>
+          <t>43565842LIMAVIZARRETA SANCHEZ, ELIZABETH DAYANA1000037029</t>
         </is>
       </c>
       <c r="R43" t="n">
-        <v>30</v>
+        <v>57</v>
       </c>
       <c r="S43" t="inlineStr">
         <is>
@@ -5367,7 +5367,7 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
+          <t>Está esperando promociones, descuentos o condiciones más favorables.</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
@@ -5380,12 +5380,12 @@
       <c r="X43" t="inlineStr"/>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Revisar despacho</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5397,7 +5397,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>83665</v>
+        <v>81109</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
@@ -5431,12 +5431,12 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>C001759933</t>
+          <t>C004191510</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>C001759933 - HIJAR ZEVALLOS MAGDALENA URBANA</t>
+          <t>C004191510 - DAMIAN SANTISTEBAN ESTHER</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -5456,11 +5456,11 @@
         <v>46235</v>
       </c>
       <c r="N44" s="3" t="n">
-        <v>46242</v>
+        <v>46246</v>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>S17718690</t>
+          <t>S17807260</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -6661,7 +6661,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>4382</v>
+        <v>4532</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
@@ -6695,12 +6695,12 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>C001002927</t>
+          <t>C001011370</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>C001002927 - ALEJANDRO GRANADOS EUSEBIO FERRER</t>
+          <t>C001011370 - LEON ACUÑA JOSE ANTONIO</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -6724,7 +6724,7 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>S17808845</t>
+          <t>S17823857</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -6777,7 +6777,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>4532</v>
+        <v>4382</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
@@ -6811,12 +6811,12 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>C001011370</t>
+          <t>C001002927</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>C001011370 - LEON ACUÑA JOSE ANTONIO</t>
+          <t>C001002927 - ALEJANDRO GRANADOS EUSEBIO FERRER</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -6840,7 +6840,7 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>S17823857</t>
+          <t>S17808845</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
